--- a/site/collomap_builder/exp1/exp1_site_data.xlsx
+++ b/site/collomap_builder/exp1/exp1_site_data.xlsx
@@ -434,12 +434,12 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>ADV</t>
+          <t>Non-final particle</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>FP</t>
+          <t>Final particle</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -449,12 +449,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>ADV -&gt; FP</t>
+          <t>Non-final particle -&gt; Final particle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>FP -&gt; ADV</t>
+          <t>Final particle -&gt; Non-final particle</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
